--- a/src/attributions/attributions_ig_traj_248.xlsx
+++ b/src/attributions/attributions_ig_traj_248.xlsx
@@ -1002,76 +1002,76 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1488752232613452</v>
+        <v>0.009573625867096921</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006311952090878249</v>
+        <v>0.07440321709106758</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.05364586990841922</v>
+        <v>-0.03398095744884147</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07972920186626041</v>
+        <v>0.01721887683540159</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00661100191344156</v>
+        <v>0.0431979219574865</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.02419526221525317</v>
+        <v>-0.03408774252550518</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.01925857314445308</v>
+        <v>-0.001791614689594271</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0595082535345634</v>
+        <v>0.05100550346383332</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.06816316826167586</v>
+        <v>0.05011645464921963</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
@@ -1089,13 +1089,13 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1159254211568217</v>
+        <v>0.03103930806990146</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.08486384533565811</v>
+        <v>-0.07353339954532497</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.02851627624775247</v>
+        <v>-0.004210452493057714</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -1104,25 +1104,25 @@
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.04132708043014814</v>
+        <v>-0.06136040472001959</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0663670566405004</v>
+        <v>-0.004844052787636132</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.01024491419204609</v>
+        <v>0.01162880202383433</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -1131,64 +1131,64 @@
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2211451979698737</v>
+        <v>0.09921842023636691</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.03422967482642116</v>
+        <v>-0.01171291414494938</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.04223171971692038</v>
+        <v>-0.07866747560744369</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.09891822501371608</v>
+        <v>-0.09837986779359371</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.02220649325481184</v>
+        <v>0.03491724284024449</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.09326897894219804</v>
+        <v>0.1379736463317847</v>
       </c>
       <c r="BI2" t="n">
         <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
         <v>-0</v>
@@ -1197,97 +1197,97 @@
         <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.02132353223135025</v>
+        <v>0.1178483961434429</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.0579932075677525</v>
+        <v>0.0440804143455828</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.01704720765299038</v>
+        <v>0.006153720968942449</v>
       </c>
       <c r="BR2" t="n">
         <v>-0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
         <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
         <v>-0</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.04657959210254212</v>
+        <v>0.03063975234739256</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.0353368193706783</v>
+        <v>0.06074598242666628</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.08904962381677516</v>
+        <v>-0.01315514905120255</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
         <v>-0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.06860903786441296</v>
+        <v>0.02426184031158844</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.008659830818778193</v>
+        <v>-0.107664305014775</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.03812625309241321</v>
+        <v>0.0346432226274996</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.0005287460617998015</v>
+        <v>0.009550515286963275</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.004111209697031854</v>
+        <v>-0.01401754217857431</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0.00119047269377804</v>
+        <v>0.005282612946112904</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
         <v>0</v>
@@ -1296,58 +1296,58 @@
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.07112173593109448</v>
+        <v>0.006414358094992253</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.004999700411400642</v>
+        <v>-0.1040369838513996</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.03090778074950343</v>
+        <v>0.04358781579642062</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.06500617381481298</v>
+        <v>0.06120416450014042</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.03552440087288096</v>
+        <v>-0.01157912217806508</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.009677812276101129</v>
+        <v>0.01309981279818616</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN2" t="n">
         <v>-0</v>
@@ -1356,25 +1356,25 @@
         <v>0</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.009305288697712214</v>
+        <v>-0.05896087480715458</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.04782515216847171</v>
+        <v>0.08375450832659316</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.04215528909124966</v>
+        <v>0.06726442848006794</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
@@ -1386,16 +1386,16 @@
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.04753042202106113</v>
+        <v>-0.06250445224211768</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.07827132690739702</v>
+        <v>-0.01275366677111754</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.01954406050415233</v>
+        <v>0.01839310848325134</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
         <v>-0</v>
@@ -1413,46 +1413,46 @@
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0.08840738539852316</v>
+        <v>0.003043504820856571</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.04797306459453922</v>
+        <v>-0.154609507245749</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.02280952684260772</v>
+        <v>0.01988331133871552</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ2" t="n">
         <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.03159570469804673</v>
+        <v>0.002126963065001807</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.09019942571040132</v>
+        <v>-0.003607001892047954</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0.02810255236131601</v>
+        <v>-0.004564646179963209</v>
       </c>
       <c r="EU2" t="n">
         <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>0</v>
@@ -1461,25 +1461,25 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.06023628329339496</v>
+        <v>0.01646920837463042</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.008691119163676091</v>
+        <v>-0.1064180777515269</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.04160476102384245</v>
+        <v>0.05022611994427444</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
         <v>-0</v>
@@ -1494,52 +1494,52 @@
         <v>0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.009884025459642294</v>
+        <v>0.04593034255212036</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.04087068667625519</v>
+        <v>-0.04221451392861184</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.08343686559044271</v>
+        <v>0.07696745653543165</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
         <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP2" t="n">
         <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.04203679141297367</v>
+        <v>-0.02412339760133516</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.01124247504929291</v>
+        <v>-0.08328071453060239</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0.04791828785046845</v>
+        <v>0.002502811432804731</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX2" t="n">
         <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
         <v>-0</v>
@@ -1548,19 +1548,19 @@
         <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.01592295058534574</v>
+        <v>0.03121883186884127</v>
       </c>
       <c r="GC2" t="n">
         <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.003757082302165309</v>
+        <v>0.04436396827175797</v>
       </c>
       <c r="GE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG2" t="n">
         <v>0</v>
@@ -2137,76 +2137,76 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1543397341879695</v>
+        <v>0.1712554368455499</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02958496910814492</v>
+        <v>0.008999055285516916</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.02491550761316389</v>
+        <v>-0.09113369296252026</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09722471334956828</v>
+        <v>0.154310953030326</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.03278966188421516</v>
+        <v>-0.03889317728863798</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.01422171630062785</v>
+        <v>-0.06813388390845658</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02331516659163542</v>
+        <v>0.08033155326493235</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0453698701740789</v>
+        <v>0.01183436762146062</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.00808991515336689</v>
+        <v>-0.006568013294504875</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2221,19 +2221,19 @@
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.06082690709256043</v>
+        <v>0.0006415341931508862</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.008067018854789177</v>
+        <v>-0.02086620724715123</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.06866837644364192</v>
+        <v>0.0028867160033818</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -2242,28 +2242,28 @@
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.02140566040512614</v>
+        <v>0.06824127610794804</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.002860060348702941</v>
+        <v>0.05010667926288733</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.07265032077702867</v>
+        <v>-0.04731265127340236</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
@@ -2272,22 +2272,22 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.2175651958330695</v>
+        <v>0.2532741989097911</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.06347116047211457</v>
+        <v>-0.02920560513697164</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.0152668860252032</v>
+        <v>-0.1337071432691033</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2299,52 +2299,52 @@
         <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.1050258831502467</v>
+        <v>0.02953571306075398</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.1276967350681869</v>
+        <v>-0.01569026253537035</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.0758212949354972</v>
+        <v>-0.06158673456468303</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.06376023340927772</v>
+        <v>0.01868003574036774</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.04140831385481724</v>
+        <v>0.08610695884080244</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.02609917198710278</v>
+        <v>0.06286350925986842</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2353,22 +2353,22 @@
         <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.09380066182914495</v>
+        <v>0.1833476739146536</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.0009871443570695581</v>
+        <v>0.009399088932078064</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002543303137248344</v>
+        <v>-0.125972343453932</v>
       </c>
       <c r="CA4" t="n">
         <v>0</v>
@@ -2377,52 +2377,52 @@
         <v>-0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.05558492994580834</v>
+        <v>-0.1056363205200401</v>
       </c>
       <c r="CF4" t="n">
         <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0001799964759417533</v>
+        <v>-0.01352704891576955</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.006461381188011335</v>
+        <v>0.07940499363171104</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.005967232970189508</v>
+        <v>-0.00797312139390367</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.001458478085489538</v>
+        <v>-0.004437155832359829</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.001464592860512544</v>
+        <v>-0.001479554423380078</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2431,52 +2431,52 @@
         <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.04410643555243494</v>
+        <v>-0.1015341174115633</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.0008416423393761932</v>
+        <v>-0.01321335621091548</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.01730418965838453</v>
+        <v>0.09705114169584803</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.03935494820933744</v>
+        <v>-0.0627024897718101</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.05980147128172481</v>
+        <v>-0.003891700683656797</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.04333768524948763</v>
+        <v>0.07424857471770975</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,31 +2485,31 @@
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.04694239505430352</v>
+        <v>-0.06123857763777165</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.02986457889957643</v>
+        <v>0.005557109242125489</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.09683601838984281</v>
+        <v>-0.07395126594113785</v>
       </c>
       <c r="DT4" t="n">
         <v>0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>-0</v>
@@ -2518,73 +2518,73 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.03814129469021303</v>
+        <v>-0.07334499490196218</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.03212914563432739</v>
+        <v>-0.01636448420101828</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.01123930828880754</v>
+        <v>0.08240636334105354</v>
       </c>
       <c r="EC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
         <v>-0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.04801623837788595</v>
+        <v>-0.05628330263292402</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.008311000499885471</v>
+        <v>-0.06086436598586707</v>
       </c>
       <c r="EK4" t="n">
-        <v>-0.06315824145296788</v>
+        <v>0.04157955318300199</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
         <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.01712514496336704</v>
+        <v>0.01566410954888896</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.03061071829969543</v>
+        <v>0.03072075058480188</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0.05061058242405494</v>
+        <v>0.0125451439684845</v>
       </c>
       <c r="EU4" t="n">
         <v>0</v>
@@ -2593,40 +2593,40 @@
         <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.03751705835371569</v>
+        <v>-0.1091419293480621</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.004093315488174765</v>
+        <v>-0.04489574178618438</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.02108465294113</v>
+        <v>0.08260278111416522</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>-0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.01879203475910941</v>
+        <v>-0.06732946830529353</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
@@ -2635,13 +2635,13 @@
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.08715168447484313</v>
+        <v>0.007014602500465257</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.04161381358752134</v>
+        <v>0.06825532549461953</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN4" t="n">
         <v>0</v>
@@ -2650,10 +2650,10 @@
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.05939267838573126</v>
+        <v>-0.1385403454254042</v>
       </c>
       <c r="FR4" t="n">
         <v>0</v>
@@ -2662,43 +2662,43 @@
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.02186477343981254</v>
+        <v>-0.02726258785615532</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.04618255422257123</v>
+        <v>0.04052983386467114</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.05156682478867555</v>
+        <v>-0.05207252106012215</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.03161612858631781</v>
+        <v>0.07492748783877898</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>0</v>
@@ -2706,19 +2706,19 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.2017888425955991</v>
+        <v>-0.1476591451633296</v>
       </c>
       <c r="C5" t="n">
         <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.09566984172833053</v>
+        <v>0.1338124783814399</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1253054673679863</v>
+        <v>0.05205399030023446</v>
       </c>
       <c r="F5" t="n">
         <v>-0</v>
@@ -2727,25 +2727,25 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1189104702026618</v>
+        <v>-0.1243421604297226</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1019244142803574</v>
+        <v>0.161109892117058</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1104293592608269</v>
+        <v>0.07138293452530482</v>
       </c>
       <c r="O5" t="n">
         <v>-0</v>
@@ -2754,31 +2754,31 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>-0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1068351354570898</v>
+        <v>-0.04079987756417201</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02455443409637274</v>
+        <v>0.02245587131981813</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.02988845194482354</v>
+        <v>0.006508540912371564</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
@@ -2787,19 +2787,19 @@
         <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.1317616181461947</v>
+        <v>-0.007189916606757953</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01373404723358118</v>
+        <v>0.1521845581504979</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02684791534839416</v>
+        <v>-0.1503901591228326</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -2811,103 +2811,103 @@
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
         <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.0571425138907023</v>
+        <v>-0.125617983823064</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0479679453134834</v>
+        <v>0.04607746116238914</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.08513938176520382</v>
+        <v>-0.1744522860669752</v>
       </c>
       <c r="AP5" t="n">
         <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.3553466709969749</v>
+        <v>-0.2523780740248965</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.03606260309084391</v>
+        <v>0.1702751404365705</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.03305277164785436</v>
+        <v>0.05209905645843434</v>
       </c>
       <c r="AY5" t="n">
         <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.05632888501780718</v>
+        <v>-0.001704332830918088</v>
       </c>
       <c r="BE5" t="n">
         <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.1417349076827029</v>
+        <v>0.04407067925762357</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.2480483364538288</v>
+        <v>0.04937651866841147</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
         <v>-0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.04378382975676044</v>
+        <v>0.08522721613236754</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.0140390230696374</v>
+        <v>0.04844303182137986</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.1035100580212537</v>
+        <v>-0.04764485850451926</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
@@ -2925,73 +2925,73 @@
         <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.2567162103371121</v>
+        <v>-0.1748708673826178</v>
       </c>
       <c r="BW5" t="n">
         <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.02662741045418527</v>
+        <v>0.06660206459972623</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.01832735017620911</v>
+        <v>0.01867714440095641</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1089740176121883</v>
+        <v>0.1552803488970471</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.04212665839891884</v>
+        <v>-0.07416015700765008</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001306496969322453</v>
+        <v>-0.02147984274304903</v>
       </c>
       <c r="CI5" t="n">
         <v>0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
         <v>-0</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.0006330889481958411</v>
+        <v>-0.005126520341116866</v>
       </c>
       <c r="CO5" t="n">
         <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.01864204886672243</v>
+        <v>-0.02721749361088284</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.01125826159253306</v>
+        <v>0.0005782749486243358</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS5" t="n">
         <v>0</v>
@@ -3006,16 +3006,16 @@
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.1100147954723156</v>
+        <v>0.1691365640691463</v>
       </c>
       <c r="CX5" t="n">
         <v>-0</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.05471305547719627</v>
+        <v>-0.08591439238197041</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.003790045568179294</v>
+        <v>-0.03079951980503292</v>
       </c>
       <c r="DA5" t="n">
         <v>-0</v>
@@ -3024,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
         <v>-0</v>
@@ -3033,52 +3033,52 @@
         <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0669725256761336</v>
+        <v>0.05715163426600715</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.04459353791867711</v>
+        <v>-0.05413023825070577</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.05259585022912761</v>
+        <v>0.007190392847274057</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.05782766197838465</v>
+        <v>0.0669690878947615</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.02699791635693409</v>
+        <v>-0.04878445498049724</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.06938141021266507</v>
+        <v>0.02247482178342971</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT5" t="n">
         <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,22 +3087,22 @@
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.09652335624919137</v>
+        <v>0.086921700702873</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.08562719246596559</v>
+        <v>-0.02228660835984682</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.005062374043623924</v>
+        <v>0.03899789474665603</v>
       </c>
       <c r="EB5" t="n">
         <v>0</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3114,70 +3114,70 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.08306072193010115</v>
+        <v>0.1585540779216957</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.03552560180710106</v>
+        <v>-0.06769071383513857</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.09643174225889732</v>
+        <v>-0.0395502911285338</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.02216002581328505</v>
+        <v>-0.08587169269490244</v>
       </c>
       <c r="EQ5" t="n">
         <v>0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.003935585556178429</v>
+        <v>-0.01814041772075069</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02858376270481193</v>
+        <v>0.02961828142310945</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU5" t="n">
         <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.1161059290644028</v>
+        <v>0.1850671095389989</v>
       </c>
       <c r="EZ5" t="n">
         <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>-0.04571407299108356</v>
+        <v>-0.08736219444579051</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.005525237673463522</v>
+        <v>-0.009487674191032558</v>
       </c>
       <c r="FC5" t="n">
         <v>0</v>
@@ -3186,25 +3186,25 @@
         <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.04352082423576756</v>
+        <v>0.07595884675806563</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.03887511664937808</v>
+        <v>0.08301817398464764</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.003280281158531146</v>
+        <v>-0.004670931722714705</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
@@ -3213,64 +3213,64 @@
         <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0228948785269883</v>
+        <v>0.1431768751169644</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.1310766822588234</v>
+        <v>0.089127419837494</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.01053178299117969</v>
+        <v>-0.0764389266928685</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
       </c>
       <c r="FV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.04686392218292912</v>
+        <v>0.1684576345645029</v>
       </c>
       <c r="GA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.04722402158464589</v>
+        <v>-0.03425707376544173</v>
       </c>
       <c r="GC5" t="n">
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.098589737730975</v>
+        <v>0.2569134810601393</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,10 +3287,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.03716882124529888</v>
+        <v>-0.04996567402448836</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.05889402576708862</v>
+        <v>-0.1671262038762914</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07591009000613824</v>
+        <v>0.2973857478324867</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,64 +3314,64 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02526441669601166</v>
+        <v>-0.1429194203941479</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.02897242378515327</v>
+        <v>-0.101964814769703</v>
       </c>
       <c r="P6" t="n">
         <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01308287818657964</v>
+        <v>0.111291574325984</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.01148623688754034</v>
+        <v>-0.1132115276314134</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01531570970063306</v>
+        <v>-0.01774981785046731</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0007722488823694022</v>
+        <v>-0.02138502215932248</v>
       </c>
       <c r="AD6" t="n">
         <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.009697745314079289</v>
+        <v>-0.2486005627568414</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.007242541824408706</v>
+        <v>0.02869287168354755</v>
       </c>
       <c r="AH6" t="n">
         <v>-0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.009657181753325368</v>
+        <v>0.06664978545866765</v>
       </c>
       <c r="AM6" t="n">
         <v>-0</v>
@@ -3395,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0164482372777186</v>
+        <v>-0.02820867137892817</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.01402000908131821</v>
+        <v>-0.01865340901757667</v>
       </c>
       <c r="AQ6" t="n">
         <v>-0</v>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1115342192350542</v>
+        <v>0.4886035892029876</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
@@ -3422,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.03806562900629869</v>
+        <v>-0.2942647904587021</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.04875157598315774</v>
+        <v>-0.2011610222265792</v>
       </c>
       <c r="AZ6" t="n">
         <v>-0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.03627771225050603</v>
+        <v>-0.04072577487320504</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,25 +3449,25 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.06671482257130028</v>
+        <v>-0.01740349125500761</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.05611205330187267</v>
+        <v>-0.1122587431834512</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.03853905649338467</v>
+        <v>0.06363294528741466</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
@@ -3476,13 +3476,13 @@
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02364058539047298</v>
+        <v>0.0994240193468147</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01717465966608096</v>
+        <v>0.05824527627649526</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3491,10 +3491,10 @@
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.05380420809177421</v>
+        <v>0.2971257762805021</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.01849187197016208</v>
+        <v>-0.09575725226005227</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.009626130295333645</v>
+        <v>-0.1069002303489354</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
@@ -3515,148 +3515,148 @@
         <v>-0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.02762513005570845</v>
+        <v>-0.1273055419787933</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.002012564282799612</v>
+        <v>0.036608427861873</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.02612644073259819</v>
+        <v>0.1000573649336454</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL6" t="n">
         <v>0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.001572324596117162</v>
+        <v>-0.03914289917811564</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.00365336446598921</v>
+        <v>0.02799775514594221</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.00551051687141719</v>
+        <v>0.03078430432487615</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.02032286390559992</v>
+        <v>-0.1295213828205139</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.006837802213101968</v>
+        <v>0.02992199786386755</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.02882748845648164</v>
+        <v>0.1261916086782875</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.03345801405159488</v>
+        <v>-0.07254983405776685</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.03608122934416567</v>
+        <v>-0.138139957115347</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.0009048471383805738</v>
+        <v>0.03537006666583684</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.00690845174317941</v>
+        <v>-0.01626688213196711</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.004166525402938957</v>
+        <v>-0.07717182827032279</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.006955147207822115</v>
+        <v>0.0294389340505027</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.02764588040787757</v>
+        <v>-0.05709606740463781</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,10 +3665,10 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0187381655148169</v>
+        <v>0.03690828654578876</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.02034467008597319</v>
+        <v>0.09990337958433256</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
@@ -3677,28 +3677,28 @@
         <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.02781516952107855</v>
+        <v>-0.04407154335092583</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.01328962260646212</v>
+        <v>0.008587456503424311</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.0304176700423284</v>
+        <v>0.03362573414211575</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
@@ -3707,22 +3707,22 @@
         <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.013018733381946</v>
+        <v>-0.01215493688323225</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.01817494190107361</v>
+        <v>-0.02788114765804464</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0008270683631312054</v>
+        <v>0.1129533598989842</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
@@ -3731,13 +3731,13 @@
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.01948476015417681</v>
+        <v>-0.1442092416608852</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
@@ -3746,43 +3746,43 @@
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.008674003653532616</v>
+        <v>0.005505974783133329</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.03110559423755292</v>
+        <v>0.09102578037579066</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01444319140441395</v>
+        <v>0.1971432346126029</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.01711024059670139</v>
+        <v>-0.0615064974149453</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01351874446343366</v>
+        <v>0.1277354737487042</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
@@ -3791,55 +3791,55 @@
         <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.005266550371329591</v>
+        <v>0.06020563300667109</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.0232812253095729</v>
+        <v>-0.0796384662859754</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.00138062191346152</v>
+        <v>-0.09052998218412588</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.004166469481758102</v>
+        <v>-0.02240047971385015</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
         <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.005889418146849242</v>
+        <v>0.1257982350161765</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,22 +3847,22 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.279124241643521</v>
+        <v>0.2607855320664335</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.06332259382534795</v>
+        <v>-0.1277286660224378</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02762894846112073</v>
+        <v>-0.02845290759022768</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
@@ -3874,22 +3874,22 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1907162918675416</v>
+        <v>0.2525698551695956</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03652675361592649</v>
+        <v>-0.08000322192783196</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03296570930158157</v>
+        <v>-0.06021094162698017</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3901,70 +3901,70 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0842227134110114</v>
+        <v>0.02952208681713724</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0002229368255991902</v>
+        <v>-0.01362600975602395</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06514595656644362</v>
+        <v>-0.08831813211798209</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1259942104877981</v>
+        <v>-0.0314275690103231</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.04420925084468882</v>
+        <v>-0.131166051263555</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.07848257797210868</v>
+        <v>-0.07831268413740101</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02155216130396037</v>
+        <v>0.09973988431581668</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.06807415932470212</v>
+        <v>-0.09225620850704286</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.03827357410075978</v>
+        <v>-0.003269200467380768</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -3982,16 +3982,16 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.3492257278969247</v>
+        <v>0.2834478509452543</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.00355701222424841</v>
+        <v>-0.2276768950889399</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1345038130050455</v>
+        <v>-0.3405049030639589</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
@@ -4000,25 +4000,25 @@
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.03300920246290733</v>
+        <v>-0.01853609476384975</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.05581374663042713</v>
+        <v>-0.02805605870965416</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1735676531394212</v>
+        <v>0.05882606193369962</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,157 +4036,157 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02978691146499432</v>
+        <v>0.02726152925015494</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.09825332270577748</v>
+        <v>0.08614738276335838</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0941963944260592</v>
+        <v>-0.006540301328475549</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.197072476710902</v>
+        <v>0.2188366240602</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.01681565687068927</v>
+        <v>-0.1361031331302198</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.06166973723403793</v>
+        <v>-0.1150034042495716</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.08767611171470337</v>
+        <v>-0.1213403971189885</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01295776117052723</v>
+        <v>0.1625167353974255</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.006527881850666439</v>
+        <v>0.01060618103704693</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01083110329922135</v>
+        <v>-0.02281401878543514</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.01425007821702101</v>
+        <v>0.02928192154939037</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.0197793589575065</v>
+        <v>0.03215251237194807</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
         <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.07254481306032003</v>
+        <v>-0.1153926062500594</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.03540277116295626</v>
+        <v>0.1702903923377896</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.007749252218819924</v>
+        <v>0.01963770231055263</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.01552554433418465</v>
+        <v>-0.07395309837329928</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.0003104113852679621</v>
+        <v>-0.01167830502688583</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.0003425891049277837</v>
+        <v>-0.1012014110814988</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -4195,25 +4195,25 @@
         <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.06000578200483908</v>
+        <v>-0.04753778059785547</v>
       </c>
       <c r="DP7" t="n">
         <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.06455456560740098</v>
+        <v>0.07843442099962625</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.06722639862900112</v>
+        <v>-0.0303886641016366</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
@@ -4222,19 +4222,19 @@
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.01088176422508598</v>
+        <v>0.02454811488022736</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.01867734357225099</v>
+        <v>0.06439306347597153</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.005377033227939417</v>
+        <v>0.01104268911710778</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
@@ -4243,58 +4243,58 @@
         <v>0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.05229549131452736</v>
+        <v>-0.07853482181913279</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.02704670919230993</v>
+        <v>0.1262159553382023</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.09251821182971544</v>
+        <v>0.02347434112177466</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.08152338177589474</v>
+        <v>-0.06807772672111304</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.08667893894024714</v>
+        <v>-0.08378375591723734</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.01626069881236129</v>
+        <v>-0.03754090568641558</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4303,25 +4303,25 @@
         <v>-0</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.07769133107128863</v>
+        <v>-0.1337854538083636</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.02266998334626571</v>
+        <v>0.1865418537922259</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.01028185361448744</v>
+        <v>0.0006863028102488193</v>
       </c>
       <c r="FC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
@@ -4333,49 +4333,49 @@
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.01051144063389798</v>
+        <v>0.1426711393867934</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.04748965459258143</v>
+        <v>0.1464844067872841</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01400474004250794</v>
+        <v>-0.001661299482522363</v>
       </c>
       <c r="FL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.002676069153934686</v>
+        <v>0.05916860197353268</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.06584445349652913</v>
+        <v>0.2004139131456817</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.03211288872499326</v>
+        <v>-0.04762021684997371</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
         <v>0</v>
@@ -4384,39 +4384,39 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.02212208209372212</v>
+        <v>-0.04413449740909142</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.03563408003848977</v>
+        <v>0.1110491267528741</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1589610711727572</v>
+        <v>0.2857746919583649</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -4425,10 +4425,10 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.04337964506746834</v>
+        <v>0.03537007003892471</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.10106543879525</v>
+        <v>-0.2590523462962723</v>
       </c>
       <c r="G8" t="n">
         <v>-0</v>
@@ -4437,13 +4437,13 @@
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1227449045020368</v>
+        <v>0.3236260504814116</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -4452,25 +4452,25 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.01494532506676126</v>
+        <v>-0.08046343143976779</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.05593671828055311</v>
+        <v>-0.207119844763047</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.02863058078650222</v>
+        <v>0.09855191790272509</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
@@ -4479,37 +4479,37 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.02229832001961994</v>
+        <v>-0.05429537937613115</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0009944783973878963</v>
+        <v>-0.071265480382568</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0003256268392576414</v>
+        <v>-0.06771747375362412</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0005517397164854005</v>
+        <v>-0.19185046540687</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.008504614147312782</v>
+        <v>0.07939889513096077</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -4524,22 +4524,22 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.02538074766034841</v>
+        <v>0.1261075475215516</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.008424205901947788</v>
+        <v>-0.03590321270631883</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.0502531428929397</v>
+        <v>-0.08781443702498574</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
@@ -4548,37 +4548,37 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1463275473736579</v>
+        <v>0.536682793244264</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.03509795254325043</v>
+        <v>-0.2479381628747725</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.109345915823353</v>
+        <v>-0.3030646692191742</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.04932863652300052</v>
+        <v>-0.1032356865571286</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
@@ -4587,10 +4587,10 @@
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.04623260542257231</v>
+        <v>0.02523571446271596</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.04530551014053272</v>
+        <v>-0.08249852919421692</v>
       </c>
       <c r="BI8" t="n">
         <v>-0</v>
@@ -4599,13 +4599,13 @@
         <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.04281810092315083</v>
+        <v>0.09271060381261344</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
@@ -4614,79 +4614,79 @@
         <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.02105778762007339</v>
+        <v>0.05598051741071496</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.004317474875009573</v>
+        <v>0.06529185197638886</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.08404362072520531</v>
+        <v>0.2966657176568378</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.024025163353162</v>
+        <v>-0.06752403124959275</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.03217315708767531</v>
+        <v>-0.1670550283776666</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
         <v>-0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.04130357840418181</v>
+        <v>-0.1482602087757987</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.002236600239076929</v>
+        <v>0.03577410811814859</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.03427002024254591</v>
+        <v>0.09379327247709286</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>5.835430320860319e-05</v>
+        <v>-0.06479243335494052</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
@@ -4695,37 +4695,37 @@
         <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0005470976653379152</v>
+        <v>0.07209929022827558</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.008606977068776637</v>
+        <v>-0.003504962134377902</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
         <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.03680334579194405</v>
+        <v>-0.1408385134544604</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.006678294474540209</v>
+        <v>0.01682759595277486</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0378188200655074</v>
+        <v>0.1273312971613949</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
@@ -4734,25 +4734,25 @@
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.005967600968891288</v>
+        <v>0.02225370653475057</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05092798024129717</v>
+        <v>-0.02281476586838516</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.00205764002187583</v>
+        <v>0.04553104920106683</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
@@ -4761,13 +4761,13 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.01912797001000105</v>
+        <v>-0.1284334160586892</v>
       </c>
       <c r="DP8" t="n">
         <v>0</v>
@@ -4776,25 +4776,25 @@
         <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.01515440308682065</v>
+        <v>0.02206513787728312</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.009579668336211303</v>
+        <v>0.1516287018265908</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.0468107666023125</v>
+        <v>-0.08591236653437558</v>
       </c>
       <c r="DY8" t="n">
         <v>-0</v>
@@ -4803,10 +4803,10 @@
         <v>-0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.02921393859205576</v>
+        <v>0.09581917862911232</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.01431956995744334</v>
+        <v>0.04027508529279056</v>
       </c>
       <c r="EC8" t="n">
         <v>0</v>
@@ -4815,25 +4815,25 @@
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.03381188172023993</v>
+        <v>-0.03079756122882678</v>
       </c>
       <c r="EH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI8" t="n">
         <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.01332405059405311</v>
+        <v>-0.03917122253372658</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.03384596103336049</v>
+        <v>0.01229790601816523</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
@@ -4842,13 +4842,13 @@
         <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.03358558061923612</v>
+        <v>-0.03997354097047578</v>
       </c>
       <c r="EQ8" t="n">
         <v>-0</v>
@@ -4857,13 +4857,13 @@
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.006699547886820608</v>
+        <v>-0.1123377051953602</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.004051194981766691</v>
+        <v>0.0110379251465177</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4875,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.03691880530666464</v>
+        <v>-0.1624301658955563</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
@@ -4884,25 +4884,25 @@
         <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.007592433114835911</v>
+        <v>0.01077013684796831</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.03584873379244093</v>
+        <v>0.1167006839372136</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02113800646607456</v>
+        <v>0.09835018060599673</v>
       </c>
       <c r="FI8" t="n">
         <v>0</v>
@@ -4911,25 +4911,25 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.01264562921169815</v>
+        <v>-0.03603830282378974</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.03154009075545897</v>
+        <v>0.1380126935321841</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.001738165228662885</v>
+        <v>0.02396480015362012</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,37 +4938,37 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.02377997533538515</v>
+        <v>-0.05132523783995464</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.02189201655433314</v>
+        <v>-0.02222808092623349</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.005932175969692238</v>
+        <v>-0.03119115905110057</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
       </c>
       <c r="GC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.01806336878785947</v>
+        <v>0.14614525878096</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -4985,46 +4985,46 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2650050552336102</v>
+        <v>0.249027327547678</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.08540261505905275</v>
+        <v>-0.1039970860381959</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.06975935624334557</v>
+        <v>0.005102570623100672</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.02848423300111132</v>
+        <v>-0.1116850877672301</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2005425909663803</v>
+        <v>0.2992648488818383</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0469943466558634</v>
+        <v>-0.09888741878714856</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04950597859014896</v>
+        <v>-0.07156062136863897</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.02572641147043984</v>
+        <v>-0.07684771733471335</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
@@ -5039,133 +5039,133 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06693374759666799</v>
+        <v>0.1042140587440149</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.01951193003928579</v>
+        <v>-0.07546360958350587</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0323346273786867</v>
+        <v>-0.09181681117021052</v>
       </c>
       <c r="X9" t="n">
-        <v>0.009331752982247294</v>
+        <v>-0.05424444718777578</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.05170185397648627</v>
+        <v>-0.05733282575330979</v>
       </c>
       <c r="AD9" t="n">
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01795248072868565</v>
+        <v>-0.1375405768613344</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.007370823556753229</v>
+        <v>-0.02843048848614434</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.01553611506841176</v>
+        <v>0.05376093495995564</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01749806933138082</v>
+        <v>0.07620863324794441</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.05718022179325975</v>
+        <v>-0.07211119139797018</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.05612006660120532</v>
+        <v>0.02997404418316774</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.03241313368255059</v>
+        <v>-0.03724727579007161</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.283709686611043</v>
+        <v>0.3603495274571381</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.03799887563040592</v>
+        <v>-0.1528886722530149</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.03156966548561439</v>
+        <v>-0.2018129319214596</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.03179248766445465</v>
+        <v>-0.166437506254554</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03857323132062866</v>
+        <v>-0.0415745301318473</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.06708321841754265</v>
+        <v>-0.07021492633720067</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1089795276012803</v>
+        <v>0.005112754921982095</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.04732587658507667</v>
+        <v>-0.09785357523193189</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,52 +5174,52 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.05716311196925</v>
+        <v>0.03624617049247352</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.05144928529924453</v>
+        <v>0.07958018939536891</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0969430017859292</v>
+        <v>0.01349651784040254</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.03554574642186482</v>
+        <v>0.0104093269296282</v>
       </c>
       <c r="BR9" t="n">
         <v>0</v>
       </c>
       <c r="BS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1270514975099279</v>
+        <v>0.1950483753457889</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0.0008018622796258022</v>
+        <v>-0.09039625522185822</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.01434587305899816</v>
+        <v>-0.06764743250590358</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.01244655151281326</v>
+        <v>-0.1303099297385667</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
@@ -5228,22 +5228,22 @@
         <v>0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.06739645866687233</v>
+        <v>-0.08965416294631859</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01058010982736738</v>
+        <v>0.09017318740581234</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.000167696443055077</v>
+        <v>-0.003744394432621063</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.02326035387194274</v>
+        <v>0.04262726363915661</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
@@ -5255,49 +5255,49 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.0004563207409788877</v>
+        <v>-0.02033285749113068</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.02145531359072898</v>
+        <v>0.08425727299422703</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.02742448701147641</v>
+        <v>0.04645953571720601</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.008938100021586157</v>
+        <v>0.01536426539140878</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.0548676370488267</v>
+        <v>-0.097334941253773</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.03137085279995845</v>
+        <v>0.1100057958453151</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.003399438728241294</v>
+        <v>0.002864686545440955</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.02270225672176187</v>
+        <v>0.07032382080882771</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
@@ -5309,19 +5309,19 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.02150088328165945</v>
+        <v>-0.05420950208610163</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.04760994177240586</v>
+        <v>0.023444112619843</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.003956014878707961</v>
+        <v>0.009200420788710457</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01211590241616265</v>
+        <v>0.02488552882447583</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
@@ -5330,31 +5330,31 @@
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.009691239470002538</v>
+        <v>0.0006608814544339273</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.03921305234909025</v>
+        <v>0.01599843077978104</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.01792211719686711</v>
+        <v>-0.1030395015917234</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.02249507212371893</v>
+        <v>-0.008142391488326442</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
@@ -5363,76 +5363,76 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.03283059838521874</v>
+        <v>-0.03421514678468975</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.01638419330862931</v>
+        <v>0.07825713762211674</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.008181814645566087</v>
+        <v>0.005783623328588454</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.03278814517648578</v>
+        <v>-0.03475952361142329</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.07838729814648575</v>
+        <v>-0.0806831319280388</v>
       </c>
       <c r="EH9" t="n">
         <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.03280448861266706</v>
+        <v>0.09199625827097606</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.05359052649747519</v>
+        <v>0.0193243416531384</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.01666918280884291</v>
+        <v>-0.036272286935615</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.04977002161745193</v>
+        <v>-0.03450502888511527</v>
       </c>
       <c r="EQ9" t="n">
         <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0247012017739537</v>
+        <v>0.0609551997732563</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.01955589592977269</v>
+        <v>0.01752867232073513</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0411708205520129</v>
+        <v>0.07581684700087714</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,19 +5444,19 @@
         <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.0545583148656341</v>
+        <v>-0.1014948293199905</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.01357296279110911</v>
+        <v>0.1283210047609431</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.008851729330875975</v>
+        <v>-0.01515149501166281</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.02804907976287273</v>
+        <v>0.05657620585043636</v>
       </c>
       <c r="FD9" t="n">
         <v>0</v>
@@ -5468,79 +5468,79 @@
         <v>0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02425699566946161</v>
+        <v>0.09704186372855188</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.03839659592325681</v>
+        <v>0.08967153372796453</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.001711482106203641</v>
+        <v>0.007460468439977981</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0.01543114945773326</v>
+        <v>0.144217944672616</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.0038207607570778</v>
+        <v>0.01292869213476163</v>
       </c>
       <c r="FR9" t="n">
         <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0171613403516136</v>
+        <v>0.1511968485040224</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.02240357659577574</v>
+        <v>-0.04224949618086624</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.021148376001634</v>
+        <v>0.004225501040959629</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.01759752878040514</v>
+        <v>-0.02898381804717588</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.05007373062138434</v>
+        <v>0.03407079336371571</v>
       </c>
       <c r="GC9" t="n">
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.02551342436708259</v>
+        <v>0.07627047447481823</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
         <v>0</v>
@@ -5554,43 +5554,43 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2387077326513741</v>
+        <v>0.2215322855406511</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.06797784265224502</v>
+        <v>-0.08079226242696226</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001104353515527399</v>
+        <v>-0.02016813462993244</v>
       </c>
       <c r="F10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1755553893213557</v>
+        <v>0.2633574869799849</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.06562201846455426</v>
+        <v>-0.0892453523440256</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.01033087717111966</v>
+        <v>-0.05682904430409131</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5608,19 +5608,19 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06227265993710771</v>
+        <v>0.05709312059146299</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01248100295046824</v>
+        <v>-0.02100990021384219</v>
       </c>
       <c r="W10" t="n">
-        <v>0.07309294609813236</v>
+        <v>-0.0298876619281884</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -5629,112 +5629,112 @@
         <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.06290120153465241</v>
+        <v>-0.0121731531045291</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.01986259900349703</v>
+        <v>-0.09044999853162897</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.01468156550347631</v>
+        <v>-0.01320952748630769</v>
       </c>
       <c r="AG10" t="n">
         <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.01928408265896196</v>
+        <v>0.06948722428070421</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.06023233303281686</v>
+        <v>-0.05501460077428859</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.04753725293071204</v>
+        <v>0.07577286768521159</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2358114980705751</v>
+        <v>0.209726271567324</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0251648680282537</v>
+        <v>-0.05016551727715616</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1222662474380745</v>
+        <v>-0.1217762517991149</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.03701665347282697</v>
+        <v>-0.0002954124804574009</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.1045919969614737</v>
+        <v>-0.03481541974007678</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.06599275087908038</v>
+        <v>-0.03824798642571543</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,16 +5743,16 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.04892852460553179</v>
+        <v>-0.007816482788425914</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.03216264329681798</v>
+        <v>0.02128912590302387</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1603512934418344</v>
+        <v>0.05874445731005184</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
@@ -5764,52 +5764,52 @@
         <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.100258298234984</v>
+        <v>0.1477717059555307</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.03564841989720731</v>
+        <v>-0.04455999138645179</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0829458903503518</v>
+        <v>-0.02206597306520466</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.06375369148944911</v>
+        <v>-0.08643282900751541</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>-0.002057769314283808</v>
+        <v>0.06991048155246572</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.01211326570539124</v>
+        <v>0.0007775842720287341</v>
       </c>
       <c r="CI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ10" t="n">
         <v>0</v>
@@ -5824,22 +5824,22 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.007045938190649382</v>
+        <v>-0.03656406692152463</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.04091356998396182</v>
+        <v>0.09783575108328708</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.04152978998435907</v>
+        <v>0.0178055101731727</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
         <v>0</v>
@@ -5851,16 +5851,16 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.04897435773996345</v>
+        <v>-0.08397317352705837</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.01407872682882558</v>
+        <v>0.08032853063722784</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.01055997007038905</v>
+        <v>0.005926514242300427</v>
       </c>
       <c r="DA10" t="n">
         <v>-0</v>
@@ -5878,16 +5878,16 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.03329815417478197</v>
+        <v>-0.04520296707651449</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01542770324616192</v>
+        <v>0.017640048201015</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01639791657613373</v>
+        <v>-0.04859064878530735</v>
       </c>
       <c r="DJ10" t="n">
         <v>-0</v>
@@ -5899,76 +5899,76 @@
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.03008037215508554</v>
+        <v>-0.03716930061347866</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.05652770668976206</v>
+        <v>-0.07453626424573065</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.02108192290297939</v>
+        <v>-0.04941527942768822</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
         <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.04520444708774131</v>
+        <v>-0.02180477969716717</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.004664726215604025</v>
+        <v>0.03619524976552568</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.01267861156450676</v>
+        <v>-0.02380579988771007</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.06565789102703237</v>
+        <v>-0.06136348149235122</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.01726239131675898</v>
+        <v>0.04812467311105083</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04920354457150818</v>
+        <v>0.03369574305309238</v>
       </c>
       <c r="EK10" t="n">
         <v>0</v>
@@ -5977,55 +5977,55 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.04520889281590022</v>
+        <v>-0.02257998965145745</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.01966675362094232</v>
+        <v>-0.001199203358449382</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.03223192967828856</v>
+        <v>-0.00859310801383986</v>
       </c>
       <c r="ET10" t="n">
         <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.05065950007802948</v>
+        <v>-0.09143585770166456</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0.009093770341052227</v>
+        <v>0.09278531423937351</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.005435958414426116</v>
+        <v>-0.01538801888340146</v>
       </c>
       <c r="FC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD10" t="n">
         <v>0</v>
@@ -6040,16 +6040,16 @@
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.03770416571436889</v>
+        <v>0.08445161908174242</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0009175467341158154</v>
+        <v>0.06760642479062147</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.03981059378440965</v>
+        <v>-0.01357754812205016</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
@@ -6061,69 +6061,69 @@
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.00144458590414132</v>
+        <v>0.00121688941597181</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.001284400071262812</v>
+        <v>0.0929289061692383</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.006469988742281124</v>
+        <v>-0.01806901786159286</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.01972838523788178</v>
+        <v>-0.06488978468003571</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.09186509288272342</v>
+        <v>0.02264964297637794</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
         <v>-0</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2878147212338333</v>
+        <v>0.3592665774559661</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06903426678540173</v>
+        <v>0.0124110029667905</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1861605570832192</v>
+        <v>-0.3185349832123135</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
@@ -6144,13 +6144,13 @@
         <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2577700144135838</v>
+        <v>0.4887661062873814</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,25 +6159,25 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.01676982683713597</v>
+        <v>-0.06469976493982263</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1812069610603313</v>
+        <v>-0.408413885587264</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02997240260031061</v>
+        <v>0.1348631657901264</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,67 +6186,67 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.01091782248889533</v>
+        <v>-0.08997640117938424</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.01066161805841402</v>
+        <v>-0.0684747771039094</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01514748725954933</v>
+        <v>-0.02099978615454538</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.03799535978859657</v>
+        <v>-0.2762934213857937</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.004067049017134807</v>
+        <v>0.09734500500817471</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI11" t="n">
         <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.04255185539692295</v>
+        <v>0.1238131272451377</v>
       </c>
       <c r="AM11" t="n">
         <v>-0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.004216380830539836</v>
+        <v>-0.05949332035183696</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.0639193299035308</v>
+        <v>-0.08840890567862766</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,37 +6255,37 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2284602772073094</v>
+        <v>0.6463937434838852</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.01842010448539014</v>
+        <v>-0.2885792206392588</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.07901639720775332</v>
+        <v>-0.1997911008837412</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.05833942486599913</v>
+        <v>-0.1126946781311991</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,64 +6294,64 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.06472983427533363</v>
+        <v>-0.02566080516115521</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.08219059373657751</v>
+        <v>-0.03750661578764619</v>
       </c>
       <c r="BI11" t="n">
         <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.04620553626372256</v>
+        <v>0.1267599079000587</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.01785785903410116</v>
+        <v>0.07541834802918621</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.005465321145655151</v>
+        <v>0.04127890339293192</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.114615607703585</v>
+        <v>0.3700263990427802</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.02948840970321008</v>
+        <v>-0.03550810160760057</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.04878079628020656</v>
+        <v>-0.182342771419829</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6360,28 +6360,28 @@
         <v>-0</v>
       </c>
       <c r="CC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD11" t="n">
         <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.0648703088395393</v>
+        <v>-0.1485052524197779</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.007721770691504358</v>
+        <v>0.03170414698786368</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.03872908045458783</v>
+        <v>0.10798569496285</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,73 +6393,73 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.003525744495956261</v>
+        <v>-0.1446464043346002</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.01611087152957932</v>
+        <v>0.1146393546140499</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.05644652086419788</v>
+        <v>0.02857141539470635</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.05921382478101779</v>
+        <v>-0.1404595684646018</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.007590635846527114</v>
+        <v>0.01524570695447108</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0401456629436726</v>
+        <v>0.1398991042049428</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.03323712693232195</v>
+        <v>-0.1112803389875733</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06211845463833868</v>
+        <v>-0.05844885863992825</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.04859796409482577</v>
+        <v>0.08664942347776897</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6468,13 +6468,13 @@
         <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.02722390994583234</v>
+        <v>-0.08910546458876216</v>
       </c>
       <c r="DP11" t="n">
         <v>0</v>
@@ -6483,94 +6483,94 @@
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.02287095351202065</v>
+        <v>-0.0005639195766592671</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.01431597885538048</v>
+        <v>0.1093306977228302</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.05460411774411725</v>
+        <v>-0.06335993665451449</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01521494923011018</v>
+        <v>-0.007427109329146578</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.03231451210163941</v>
+        <v>0.0352411578116134</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.06896587327047683</v>
+        <v>-0.03320885329837635</v>
       </c>
       <c r="EH11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI11" t="n">
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.02754018855389256</v>
+        <v>-0.02386518241475493</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0253394665324788</v>
+        <v>0.02759106305415946</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO11" t="n">
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.05035544475187786</v>
+        <v>-0.05758744597421768</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.03500058140180162</v>
+        <v>-0.07571519355732911</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.008463769422931347</v>
+        <v>-0.008201805572983724</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
@@ -6582,46 +6582,46 @@
         <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.05914737327037439</v>
+        <v>-0.1689420317745762</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.001121468935411549</v>
+        <v>-0.006821154732513475</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03988739638894542</v>
+        <v>0.1216136351736869</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.03157828800321573</v>
+        <v>0.113972084665418</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.007263258386767567</v>
+        <v>-0.06401186692973805</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03666540696353879</v>
+        <v>0.1740780511956319</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
@@ -6633,10 +6633,10 @@
         <v>0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.000422044898886936</v>
+        <v>0.009837011797909613</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,37 +6645,37 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.002354695548638968</v>
+        <v>-0.007780681991905951</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.04851509601175726</v>
+        <v>-0.0723317750183132</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0005669519955003551</v>
+        <v>-0.02381991724614782</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.04211418995605395</v>
+        <v>0.1680208705088072</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4870340664615532</v>
+        <v>0.3451182324101872</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,16 +6701,16 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1171038079518017</v>
+        <v>-0.02415007276200525</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4436249964418046</v>
+        <v>-0.1423975481477552</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -6719,7 +6719,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4564442769178869</v>
+        <v>0.4556398729406052</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,25 +6728,25 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05570592675916219</v>
+        <v>-0.1057542333602102</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4518573142021146</v>
+        <v>-0.2037387679502438</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03678668043720053</v>
+        <v>0.0994621737550056</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -6755,16 +6755,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.08439262822239568</v>
+        <v>-0.1181451646230026</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.01567068857811676</v>
+        <v>-0.01165391202914747</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -6773,19 +6773,19 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.02363507836424826</v>
+        <v>-0.03181093238320283</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.01012467495818293</v>
+        <v>-0.2802260515972894</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.03447034086699631</v>
+        <v>-0.0004806981102348303</v>
       </c>
       <c r="AH12" t="n">
         <v>-0</v>
@@ -6800,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.08346482370634739</v>
+        <v>0.03391320067782991</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
@@ -6809,10 +6809,10 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.001425139274130004</v>
+        <v>-0.04382687751844315</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.08288815890890448</v>
+        <v>0.01800998439388342</v>
       </c>
       <c r="AQ12" t="n">
         <v>-0</v>
@@ -6824,10 +6824,10 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4142823062989933</v>
+        <v>0.490930550772916</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,16 +6836,16 @@
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.07056162875261536</v>
+        <v>-0.2412630341333792</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.2195072107427806</v>
+        <v>-0.1060183635823349</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>0</v>
@@ -6854,7 +6854,7 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1084983479853896</v>
+        <v>-0.03244371999040717</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,52 +6863,52 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1511296373082835</v>
+        <v>-0.01743696709524062</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.1920463743209763</v>
+        <v>-0.08854328880803962</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1430673738132707</v>
+        <v>0.0555858806580355</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.003506804419984493</v>
+        <v>0.08095184223925117</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.01774829638850664</v>
+        <v>-0.0353695774531211</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2174578064331273</v>
+        <v>0.2645884054932645</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
@@ -6917,10 +6917,10 @@
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.07027843473932166</v>
+        <v>-0.07607225122038919</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.1317131469424722</v>
+        <v>-0.1065766498934343</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
@@ -6935,22 +6935,22 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.08493679991571336</v>
+        <v>-0.1128628071677499</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.005132296706541574</v>
+        <v>0.02940671068759908</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.107260316561954</v>
+        <v>0.05005876308788209</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,100 +6962,100 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.411111576022698e-05</v>
+        <v>-0.1176648399683078</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.01656313510158922</v>
+        <v>0.0987659328249483</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.02173635870421967</v>
+        <v>0.09696302121904032</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.06794519309467903</v>
+        <v>-0.1132667735478171</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.002517826506811512</v>
+        <v>0.008266387471978583</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.1129463761574095</v>
+        <v>0.07134993351079165</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.04002326517017469</v>
+        <v>-0.04182103570936625</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0444566794875837</v>
+        <v>-0.1773522024170269</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0.001614683906987056</v>
+        <v>0.05430905562071246</v>
       </c>
       <c r="DK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.006081052987154392</v>
+        <v>-0.006789881564130029</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.03351720870604942</v>
+        <v>-0.06165173203514228</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0.00651404814989466</v>
+        <v>0.07945600496514979</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7064,13 +7064,13 @@
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.05777594466092893</v>
+        <v>-0.0203989119697206</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
@@ -7079,106 +7079,106 @@
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01639577769065341</v>
+        <v>-0.0676568575607339</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.05440360332127209</v>
+        <v>0.03633715307927934</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.09693440032671177</v>
+        <v>-0.04598912915854268</v>
       </c>
       <c r="EH12" t="n">
         <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.02439302318152298</v>
+        <v>0.02204225341916105</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.1195640580710318</v>
+        <v>-0.009853383573066175</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.02990216264525762</v>
+        <v>-0.005227696832770167</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.01296633880913288</v>
+        <v>-0.01220162516658875</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.07094629067274934</v>
+        <v>0.1364584260180013</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.06543195927951648</v>
+        <v>-0.130932432158351</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.006229404879093165</v>
+        <v>-0.002061555924192711</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.1024537790435004</v>
+        <v>0.03987951912620769</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.002535719417640378</v>
+        <v>0.2075057372435904</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
@@ -7187,16 +7187,16 @@
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.008508884200727705</v>
+        <v>-0.08888362194263089</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.05172385674770193</v>
+        <v>0.1169911234280748</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
@@ -7205,46 +7205,46 @@
         <v>0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.004963051982165477</v>
+        <v>0.01095474566180105</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.008810654514323803</v>
+        <v>-0.02433236845990461</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.03438754936987051</v>
+        <v>-0.04959525460895942</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.04462418624405818</v>
+        <v>-0.0392241248176862</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.05108333755087999</v>
+        <v>0.06229019800014492</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1555227955103367</v>
+        <v>0.3740873085411197</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,25 +8408,25 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.08280241633837762</v>
+        <v>-0.01212069175337799</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07228254118439849</v>
+        <v>-0.1420221622722794</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1280013609926359</v>
+        <v>0.4550155857997566</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -8435,25 +8435,25 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05768573777505789</v>
+        <v>-0.1030346101625517</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.07598714090533507</v>
+        <v>-0.1872297503630286</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01378244307605709</v>
+        <v>0.08850790259557874</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -8462,40 +8462,40 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.004451178988662641</v>
+        <v>-0.08737791763617689</v>
       </c>
       <c r="X15" t="n">
-        <v>0.009296517155136153</v>
+        <v>-0.01195679459117023</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.004937052603166965</v>
+        <v>-0.03445648712941773</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.01397086337945391</v>
+        <v>-0.2456376296061947</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.01246458326384953</v>
+        <v>0.01208147322881906</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
         <v>-0</v>
@@ -8507,22 +8507,22 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.01048426267962558</v>
+        <v>0.03864887039576933</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.008843058167262783</v>
+        <v>-0.03478953138166604</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.01472490147678882</v>
+        <v>0.004348853773135694</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8531,28 +8531,28 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.1072825700670186</v>
+        <v>0.4082565567656767</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.02880010261672456</v>
+        <v>-0.2569226983256364</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.02119212093019258</v>
+        <v>-0.1019174011449789</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
         <v>0</v>
@@ -8561,7 +8561,7 @@
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.03149636970574076</v>
+        <v>-0.007966828915457077</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,52 +8570,52 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.05775229627875221</v>
+        <v>0.003299825105484479</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.05909104473704765</v>
+        <v>-0.06672767056896817</v>
       </c>
       <c r="BI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.03556435611813727</v>
+        <v>0.03790515352353375</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0160377211932141</v>
+        <v>0.05412149956945281</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01704690532514525</v>
+        <v>-0.02904912448350688</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.05103091105067987</v>
+        <v>0.2284431608214726</v>
       </c>
       <c r="BW15" t="n">
         <v>0</v>
@@ -8624,10 +8624,10 @@
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.01218046926464564</v>
+        <v>-0.06484531704446789</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0.01384008897907786</v>
+        <v>-0.108101791999787</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
@@ -8636,31 +8636,31 @@
         <v>-0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.02622308846222178</v>
+        <v>-0.106248834828522</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.007127736093176795</v>
+        <v>0.02637823890535754</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.01772200217820961</v>
+        <v>0.05235108424751526</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
@@ -8669,52 +8669,52 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.0008607606247808709</v>
+        <v>-0.1167963372686887</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.007075855757484145</v>
+        <v>0.1418910920064637</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.01179765717120735</v>
+        <v>0.06948314519810558</v>
       </c>
       <c r="CS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.01997228527183853</v>
+        <v>-0.1042914444843911</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.006098553888960175</v>
+        <v>0.01336787605902164</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.01817422480022265</v>
+        <v>0.07393732256271993</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>0</v>
@@ -8723,22 +8723,22 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.03236358042313904</v>
+        <v>-0.07613463879940778</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.05139714038333401</v>
+        <v>-0.2088158290936235</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.01369322867674388</v>
+        <v>0.0664830782668345</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
@@ -8747,28 +8747,28 @@
         <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.005787316285419271</v>
+        <v>-0.01453139399809695</v>
       </c>
       <c r="DP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.01937102480609069</v>
+        <v>-0.04380413370108927</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0.009748317299426336</v>
+        <v>0.04598420032442908</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
@@ -8777,49 +8777,49 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.02951577427682513</v>
+        <v>-0.008128724834928856</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01498315768491325</v>
+        <v>-0.05739258479727879</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.01825960522851271</v>
+        <v>0.02186635189298738</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.0315053328593496</v>
+        <v>-0.04910027289638845</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.00944317674849344</v>
+        <v>0.009966225733988959</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.01334605781814872</v>
+        <v>-0.0008290111176221996</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
@@ -8828,82 +8828,82 @@
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.01243019102766987</v>
+        <v>-0.03263751016830274</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.002243096035829807</v>
+        <v>-0.01666909488296208</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.01165242559899074</v>
+        <v>0.1081606505080878</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
       </c>
       <c r="EW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.0208915055260241</v>
+        <v>-0.1236182570442468</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.009264301360075101</v>
+        <v>0.001119420975175839</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.02170654796978215</v>
+        <v>0.04480882699908054</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.01511337365004362</v>
+        <v>0.1682489665630392</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.0113268961668335</v>
+        <v>-0.08182097191585727</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.01985781488408164</v>
+        <v>0.1168730928665216</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
@@ -8912,63 +8912,63 @@
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>7.644719732458803e-05</v>
+        <v>0.001766033095943371</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.001509859052916248</v>
+        <v>-0.008890543018079875</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.01880918805336776</v>
+        <v>-0.02826654740530361</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.001820653164314721</v>
+        <v>-0.03526500023485375</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
         <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.005457780234660795</v>
+        <v>0.06675703004937075</v>
       </c>
       <c r="GE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF15" t="n">
         <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.1266462604957166</v>
+        <v>0.2568294364946774</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0359596502453245</v>
+        <v>0.08360029537802897</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1458807809284861</v>
+        <v>-0.1124021230301778</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -8989,10 +8989,10 @@
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1005695273084039</v>
+        <v>0.2217196001047798</v>
       </c>
       <c r="K16" t="n">
         <v>-0</v>
@@ -9001,43 +9001,43 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.002737779122467324</v>
+        <v>-0.007165351043765546</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0997243053547566</v>
+        <v>-0.1079803910484537</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>-0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01760666690443216</v>
+        <v>-0.06928175277144705</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.03898100455986269</v>
+        <v>-0.04621480493013201</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.02367567826519899</v>
+        <v>-0.08056909819103956</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.01516222809156062</v>
+        <v>0.0545615304003013</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -9055,43 +9055,43 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.02746700724001907</v>
+        <v>-0.03953367418522752</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.02875747820365326</v>
+        <v>0.05219803461472458</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.02170311454758471</v>
+        <v>0.01635961694893267</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.007094937415410008</v>
+        <v>0.0310684134670413</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.01299687962429524</v>
+        <v>0.01725490832228489</v>
       </c>
       <c r="AQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -9100,25 +9100,25 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.08472652476482592</v>
+        <v>-0.0180578642833223</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.1007914678233191</v>
+        <v>0.08887558904301493</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.08600565149370705</v>
+        <v>-0.007113253437926324</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
         <v>0</v>
@@ -9127,22 +9127,22 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.01499549256361632</v>
+        <v>0.1617831854512066</v>
       </c>
       <c r="BD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.01190784752073141</v>
+        <v>-0.02019540684000256</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.04702454220862393</v>
+        <v>0.002295561210419389</v>
       </c>
       <c r="BI16" t="n">
         <v>0</v>
@@ -9154,10 +9154,10 @@
         <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.007487808577764449</v>
+        <v>-0.06679451029213296</v>
       </c>
       <c r="BM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
@@ -9166,37 +9166,37 @@
         <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.003610416424803363</v>
+        <v>-0.1113391538630767</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.008104688305153049</v>
+        <v>0.03653506681344443</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.03643594286452657</v>
+        <v>-0.02642080760106553</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
       </c>
       <c r="BW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX16" t="n">
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.03598242985426318</v>
+        <v>-0.0702652693062062</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.06421245250715174</v>
+        <v>-0.1104025499013803</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9205,10 +9205,10 @@
         <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>-0.02249073403637856</v>
+        <v>-0.06422544393623388</v>
       </c>
       <c r="CE16" t="n">
         <v>0</v>
@@ -9220,13 +9220,13 @@
         <v>0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.01066464430794283</v>
+        <v>0.007021126430780321</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.04343561869056956</v>
+        <v>0.03115380220022167</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
@@ -9235,25 +9235,25 @@
         <v>-0</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.004126862283695319</v>
+        <v>0.01181028276288585</v>
       </c>
       <c r="CN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.06820944344543946</v>
+        <v>0.08373939567032432</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.001346799260798693</v>
+        <v>-0.04380478783386278</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
         <v>-0</v>
@@ -9262,7 +9262,7 @@
         <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>-0.02108001772460196</v>
+        <v>-0.06726026660128644</v>
       </c>
       <c r="CW16" t="n">
         <v>-0</v>
@@ -9274,40 +9274,40 @@
         <v>-0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.01460815439289092</v>
+        <v>0.004563328884568592</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03937246904179714</v>
+        <v>0.03598994833441783</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE16" t="n">
-        <v>-0.0001534932277220459</v>
+        <v>-0.005146031250466448</v>
       </c>
       <c r="DF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.03079357996395915</v>
+        <v>-0.06032322361351384</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.001550474019576347</v>
+        <v>0.01431398112090277</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
         <v>0</v>
@@ -9316,7 +9316,7 @@
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0.0005372762060466832</v>
+        <v>-0.03987372890085466</v>
       </c>
       <c r="DO16" t="n">
         <v>0</v>
@@ -9325,13 +9325,13 @@
         <v>0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.03730876190525402</v>
+        <v>-0.05332094162376333</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.01723860783134225</v>
+        <v>0.08169112504517606</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
@@ -9340,37 +9340,37 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW16" t="n">
-        <v>-0.008746059748456648</v>
+        <v>0.02465871043844876</v>
       </c>
       <c r="DX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY16" t="n">
         <v>-0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.01650795672862657</v>
+        <v>0.1237911810008313</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.03860945368572078</v>
+        <v>0.06352424167544639</v>
       </c>
       <c r="EC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE16" t="n">
         <v>0</v>
       </c>
       <c r="EF16" t="n">
-        <v>-0.02203262574153988</v>
+        <v>0.003466002153019663</v>
       </c>
       <c r="EG16" t="n">
         <v>0</v>
@@ -9382,22 +9382,22 @@
         <v>0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>-0.003408451035381646</v>
+        <v>-0.02625681375732344</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.04728923408716374</v>
+        <v>0.0510532135942809</v>
       </c>
       <c r="EL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
         <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>-0.01277627041603102</v>
+        <v>-0.03844273207820576</v>
       </c>
       <c r="EP16" t="n">
         <v>0</v>
@@ -9406,13 +9406,13 @@
         <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.02803751493072065</v>
+        <v>0.006067814825159359</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.002817743768328517</v>
+        <v>0.04406886628997701</v>
       </c>
       <c r="EU16" t="n">
         <v>0</v>
@@ -9424,7 +9424,7 @@
         <v>-0</v>
       </c>
       <c r="EX16" t="n">
-        <v>-0.01808398236400945</v>
+        <v>-0.05967497713790787</v>
       </c>
       <c r="EY16" t="n">
         <v>0</v>
@@ -9436,22 +9436,22 @@
         <v>0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.02408577528846209</v>
+        <v>-0.006747037493913817</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.04115578127544132</v>
+        <v>0.04533085295682484</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.007376195651755181</v>
+        <v>0.127769368547643</v>
       </c>
       <c r="FH16" t="n">
         <v>-0</v>
@@ -9460,13 +9460,13 @@
         <v>0</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.01202097803954294</v>
+        <v>-5.861337664423544e-05</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0.002121784118489793</v>
+        <v>0.1059281336776556</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
@@ -9478,10 +9478,10 @@
         <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.0006546982649096399</v>
+        <v>0.003074093359563177</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,13 +9490,13 @@
         <v>0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.0006216824476783274</v>
+        <v>0.001590208613466223</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.01139849522618542</v>
+        <v>0.04096364891334509</v>
       </c>
       <c r="FV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW16" t="n">
         <v>-0</v>
@@ -9505,28 +9505,28 @@
         <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.00460258118434362</v>
+        <v>0.0725763631748053</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.01054367872908787</v>
+        <v>0.07896609230274053</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
         <v>0</v>
